--- a/data_extactor/batch_10_fa/batch_0046_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0046_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Neurologists (متخصصان مغز و اعصاب)</t>
+          <t>متخصصان مغز و اعصاب (Neurologists)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adult Neurologist | Adult and Pediatric Neurologist | General Neurologist | Neurologist | Pediatric Neurologist | Physician</t>
+          <t>متخصص مغز و اعصاب بزرگسالان | متخصص مغز و اعصاب بزرگسالان و کودکان | متخصص عمومی مغز و اعصاب | متخصص مغز و اعصاب | متخصص مغز و اعصاب کودکان | پزشک</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nuesoft Technologies NueMD | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | e-MDs software | eClinicalWorks EHR software | simplifyMD</t>
+          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nuesoft Technologies NueMD | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | تفکر انتقادی | درک مطلب | نظارت | نوشتن | یادگیری فعال | علوم | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | کامپیوتر و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | رایانه و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک نوشتاری | بیان نوشتاری | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | تجسم | اصالت | توجه انتخابی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | تجسم | اصالت | توجه انتخابی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | تکرار تصمیم‌گیری | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل محیطی | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | در معرض بیماری یا عفونت بودن | نتایج کاری و خروجی‌های سایر کارکنان | سلامت و ایمنی سایر کارکنان | سطح رقابت | صرف زمان برای نشستن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | فراوانی تصمیم‌گیری | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | سطح رقابت | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Chiropractors | Clinical Neuropsychologists | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neuropsychologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Psychiatrists | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | عصب‌روان‌شناسان بالینی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | عصب‌روان‌شناسان | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Obstetricians and Gynecologists (متخصصان زنان و زایمان)</t>
+          <t>متخصصان زنان و زایمان (Obstetricians and Gynecologists)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GYN (Gynecologist) | MD (Medical Doctor) | OB (Obstetrician) | OB/GYN (Obstetrician Gynecologist) | OBGYN (Obstetrician and Gynecologist) | OBGYN MD (Obstetrics Gynecology Medical Doctor) | OBGYN Physician (Obstetrics and Gynecology Physician) | Physician | Physician GYN (Physician Gynecologist) | Physician OB (Physician Obstetrician)</t>
+          <t>GYN (متخصص زنان) | MD (دکترای پزشکی) | OB (متخصص زایمان) | OB/GYN (متخصص زنان و زایمان) | OBGYN (متخصص زنان و زایمان) | پزشک زنان و زایمان (OBGYN MD) | پزشک زنان و زایمان (OBGYN Physician) | پزشک | پزشک متخصص زنان (Physician GYN) | پزشک متخصص زایمان (Physician OB)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AS Software AS-OBGYN | Acrendo Medical Software Ob/Gyn EMR | Allscripts Professional EHR | Alteer Premiere | Bizmatics PrognoCIS EMR | ChartWare EMR | Computer Systems Company R4 ACERT | نرم‌افزار ایمیل | Epic Systems | Greenway Medical Technologies PrimeSUITE | نرم‌افزار MEDITECH | MedcomSoft Record | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Practice Partner Total Practice Partner | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | digiChart OB-GYN | e-MDs software | eClinicalWorks EHR software</t>
+          <t>AS Software AS-OBGYN | Acrendo Medical Software Ob/Gyn EMR | Allscripts Professional EHR | Alteer Premiere | Bizmatics PrognoCIS EMR | ChartWare EMR | Computer Systems Company R4 ACERT | نرم‌افزار ایمیل | Epic Systems | Greenway Medical Technologies PrimeSUITE | نرم‌افزار MEDITECH | MedcomSoft Record | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Practice Partner Total Practice Partner | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | digiChart OB-GYN | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخنوری | نوشتن | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | کامپیوتر و الکترونیک | آموزش و پرورش | شیمی | اداری | مدیریت و اداره | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | رایانه و الکترونیک | آموزش و پرورش | شیمی | اداری | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک نوشتاری | درک شفاهی | بیان نوشتاری | دید نزدیک | وضوح گفتار | تشخیص گفتار | نظم‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | مهارت انگشتان | مهارت دستی | توجه انتخابی | تشخیص رنگ بصری | دقت کنترل | اشتراک زمانی | سرعت ادراکی | سرعت بستار</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | مهارت انگشتان | مهارت دستی | توجه انتخابی | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | تکرار تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض بیماری یا عفونت بودن | نتایج کاری و خروجی‌های سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | فشار زمانی | سلامت و ایمنی سایر کارکنان | پیامد خطا | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای ایستادن</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | فشار زمانی | سلامت و ایمنی سایر کارکنان | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Hospitalists | Naturopathic Physicians | Neurologists | Nurse Midwives | Nurse Practitioners | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Registered Nurses | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران ثبت‌شده | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pediatricians, General (متخصصان کودکان، عمومی)</t>
+          <t>متخصصان کودکان، عمومی (Pediatricians, General)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Developmental Pediatrician | Emergency Room Pediatrician (ER Pediatrician) | General Pediatrician | Group Practice Pediatrician | Medical Doctor (MD) | Pediatric Emergency Medicine Physician | Pediatric Physician | Physician | Primary Care Pediatrician</t>
+          <t>متخصص رشد و تکامل کودکان | متخصص کودکان اورژانس (ER Pediatrician) | متخصص عمومی کودکان | متخصص کودکان مطب گروهی | دکترای پزشکی (MD) | پزشک طب اورژانس کودکان | پزشک کودکان | پزشک | متخصص کودکان مراقبت اولیه</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Advanced Data Systems MedicsDocAssistant for Pediatrics | Allscripts Professional EHR | ChartWare EMR | نرم‌افزار مرجع دارویی | EMR Experts Pediatric EMR | نرم‌افزار ایمیل | Epic Systems | نرم‌افزار Epic Systems | نرم‌افزار MEDITECH | MedcomSoft Record | پایگاه‌های داده اطلاعات پزشکی | Microsoft Access | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | SOAPware EMR | نرم‌افزار زمان‌بندی | StatCoder.com STAT E&amp;M Coder | نرم‌افزار مرورگر وب | e-MDs software | e-MedRecords CompuKID | eClinicalWorks EHR software</t>
+          <t>Advanced Data Systems MedicsDocAssistant for Pediatrics | Allscripts Professional EHR | ChartWare EMR | نرم‌افزار مرجع دارویی | EMR Experts Pediatric EMR | نرم‌افزار ایمیل | Epic Systems | نرم‌افزار Epic Systems | نرم‌افزار MEDITECH | MedcomSoft Record | پایگاه‌های داده اطلاعات پزشکی | Microsoft Access | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | SOAPware EMR | نرم‌افزار زمان‌بندی | StatCoder.com STAT E&amp;M Coder | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | e-MedRecords CompuKID | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | علوم | نوشتن | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | اشتراک زمانی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت بودن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | نزدیکی فیزیکی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل محیطی | نتایج کاری و خروجی‌های سایر کارکنان | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | پیامد خطا | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Advanced Practice Psychiatric Nurses | Allergists and Immunologists | Cardiologists | Clinical Nurse Specialists | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Hospitalists | Naturopathic Physicians | Neurologists | Nurse Midwives | Nurse Practitioners | Obstetricians and Gynecologists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Psychiatrists | Urologists</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان قلب | متخصصان پرستاری بالینی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Physicians, Pathologists (پزشکان، آسیب‌شناسان)</t>
+          <t>پزشکان، آسیب‌شناسان (Physicians, Pathologists)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anatomic Pathologist | Cytopathologist | Dermatopathologist | Forensic Pathologist | Hematopathologist | Neuropathologist | Oral Pathologist | Pathologist | Surgical Pathologist</t>
+          <t>متخصص آسیب‌شناسی تشریحی | متخصص سیتوپاتولوژی | متخصص آسیب‌شناسی پوست | متخصص آسیب‌شناسی قانونی | متخصص آسیب‌شناسی خون | متخصص آسیب‌شناسی اعصاب | متخصص آسیب‌شناسی دهان | متخصص آسیب‌شناسی | متخصص آسیب‌شناسی جراحی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | سخنوری | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | کامپیوتر و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان نوشتاری | درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال قیاسی | دید نزدیک | وضوح گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی | توانایی عددی | استدلال ریاضی | اصالت</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | فشار زمانی | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف مشابه | تماس با دیگران | سطح رقابت | صرف زمان برای انجام حرکات تکراری | در معرض بیماری یا عفونت بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | فشار زمانی | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | سطح رقابت | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Clinical Neuropsychologists | Cytogenetic Technologists | Cytotechnologists | Dermatologists | Emergency Medicine Physicians | General Internal Medicine Physicians | Histotechnologists | Medical Scientists, Except Epidemiologists | Medical and Clinical Laboratory Technicians | Medical and Clinical Laboratory Technologists | Neurologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Radiologists | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | عصب‌روان‌شناسان بالینی | تکنولوژیست‌های سیتوژنتیک | سیتوتکنولوژیست‌ها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | هیستوتکنولوژیست‌ها | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | متخصصان مغز و اعصاب | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | رادیولوژیست‌ها | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Psychiatrists (روان‌پزشکان)</t>
+          <t>روان‌پزشکان (Psychiatrists)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adult Psychiatrist | Child Psychiatrist | Consulting Psychiatrist | Medical Doctor (MD) | Outpatient Psychiatrist | Prison Psychiatrist | Psychiatrist | Staff Psychiatrist</t>
+          <t>روان‌پزشک بزرگسالان | روان‌پزشک کودک | روان‌پزشک مشاور | دکترای پزشکی (MD) | روان‌پزشک سرپایی | روان‌پزشک زندان | روان‌پزشک | روان‌پزشک کادر درمان</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADL Data Systems OptimumClinicals Electronic Health Record | Advantage Software Psych Advantage | Allscripts Sunrise | Blumenthal Software PBSW24 | Cerner ProFile | Computer Assisted Diagnostic Interview CADI software | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic EpicCare Inpatient Clinical System | Epic Systems | FifthWalk BillingTracker Pro | GE Healthcare Centricity EMR | ICANotes | Integrated Systems Management OmniMD | MDofficeManager MediVoxx | MEDITECH Behavioral Health Clinicals | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Netsmart Technologies Avatar Clinical Workstation CWS | نرم‌افزار مدیریت مطب PMS | نرم‌افزار ارزیابی روان‌پزشکی | پایگاه‌های داده اطلاعات روان‌پزشکی | Sigmund Software Sigmund Enterprise Management | SoftPsych Psychiatric Diagnosis | Texas Medical Software SpringCharts EMR | UnisonCare UniCharts | نرم‌افزار واقعیت مجازی | نرم‌افزار مرورگر وب | eClinicalWorks EHR software</t>
+          <t>ADL Data Systems OptimumClinicals Electronic Health Record | Advantage Software Psych Advantage | Allscripts Sunrise | Blumenthal Software PBSW24 | Cerner ProFile | Computer Assisted Diagnostic Interview CADI software | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic EpicCare Inpatient Clinical System | Epic Systems | FifthWalk BillingTracker Pro | GE Healthcare Centricity EMR | ICANotes | Integrated Systems Management OmniMD | MDofficeManager MediVoxx | MEDITECH Behavioral Health Clinicals | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Netsmart Technologies Avatar Clinical Workstation CWS | نرم‌افزار مدیریت مطب PMS | نرم‌افزار ارزیابی روان‌پزشکی | پایگاه‌های داده اطلاعات روان‌پزشکی | Sigmund Software Sigmund Enterprise Management | SoftPsych Psychiatric Diagnosis | Texas Medical Software SpringCharts EMR | UnisonCare UniCharts | نرم‌افزار واقعیت مجازی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخنوری | درک مطلب | نوشتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و مردم‌شناسی | مدیریت و اداره | فلسفه و الهیات | کامپیوتر و الکترونیک</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | دید نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | حافظه‌سپاری | سرعت بستار</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | حفظ کردن | سرعت بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | تکرار تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فشار زمانی | پیامد خطا | اهمیت دقیق یا صحیح بودن | موقعیت‌های تعارض | در معرض بیماری یا عفونت بودن | برخورد با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فشار زمانی | پیامد خطا | اهمیت دقیق یا درست بودن | موقعیت‌های تعارض | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Cardiologists | Clinical Neuropsychologists | Clinical Nurse Specialists | Clinical and Counseling Psychologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Genetic Counselors | Naturopathic Physicians | Neurologists | Neuropsychologists | Nurse Practitioners | Obstetricians and Gynecologists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Psychiatric Technicians</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان قلب | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | عصب‌روان‌شناسان | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | تکنسین‌های روانپزشکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Radiologists (رادیولوژیست‌ها)</t>
+          <t>رادیولوژیست‌ها (Radiologists)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Attending Physician | Diagnostic Radiologist | Interventional Neuroradiologist | Interventional Radiologist | Musculoskeletal Specialty Radiologist (MSK Specialty Radiologist) | Neuroradiologist | Nuclear Medicine Physician | Nuclear Medicine Specialist | Physician | Radiologist</t>
+          <t>پزشک معالج ارشد | متخصص رادیولوژی تشخیصی | متخصص نورورادیولوژی مداخله‌ای | متخصص رادیولوژی مداخله‌ای | رادیولوژیست تخصصی اسکلتی‌عضلانی (MSK) | متخصص نورورادیولوژی | پزشک طب هسته‌ای | متخصص طب هسته‌ای | پزشک | متخصص رادیولوژی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ACOM Solutions RAPID EMR | Advanced Data Systems MedicsRis | Allscripts PM | Allscripts Professional EHR | Alteer Office | Automatic Data Processing AdvancedMD EHR | Avreo Radiology Workflow Solutions | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار تحلیل تصویر به کمک کامپیوتر | نرم‌افزار تصویربرداری پزشکی DICOM | نرم‌افزار پردازش تصویر دیجیتال | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | Fujifilm Synapse | GE Healthcare Centricity EMR | GE Healthcare Centricity Practice Solution | GE Healthcare ViewPoint for Radiology | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | Hosted PACS Solutions | IOS Health Systems Medios EHR | Infinite Radiology Opal-RAD | Kareo Practice Management | نرم‌افزار MEDITECH | MIM Software MIMcardiac | MIM Software MIMfusion | MIM Software MIMneuro | Maplewood Software StaffReady | McKesson Practice Plus | McKesson Radiology Manager | Merge Healthcare Merge RIS | Microsoft Excel | Microsoft Word | Modernizing Medicine Practice Management | نرم‌افزار اصلاح حرکت | NextGen Healthcare Information Systems EMR | NextGen Healthcare NextGen Practice Management | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار مدیریت بیمار | پایگاه‌های داده موجودی رادیودارو | RamSoft PowerServer RIS/PACS | SOAPware EMR | نرم‌افزار زمان‌بندی | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | نرم‌افزار مرورگر وب | athenahealth athenaCollector | eClinicalWorks EHR software | mPlexus DICOM RadiX | medQ Q/ris | simplifyMD</t>
+          <t>ACOM Solutions RAPID EMR | Advanced Data Systems MedicsRis | Allscripts PM | Allscripts Professional EHR | Alteer Office | Automatic Data Processing AdvancedMD EHR | Avreo Radiology Workflow Solutions | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار تحلیل تصویر به کمک کامپیوتر | نرم‌افزار تصویربرداری پزشکی DICOM | نرم‌افزار پردازش تصویر دیجیتال | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | Fujifilm Synapse | GE Healthcare Centricity EMR | GE Healthcare Centricity Practice Solution | GE Healthcare ViewPoint for Radiology | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | Hosted PACS Solutions | IOS Health Systems Medios EHR | Infinite Radiology Opal-RAD | Kareo Practice Management | نرم‌افزار MEDITECH | MIM Software MIMcardiac | MIM Software MIMfusion | MIM Software MIMneuro | Maplewood Software StaffReady | McKesson Practice Plus | McKesson Radiology Manager | Merge Healthcare Merge RIS | Microsoft Excel | Microsoft Word | Modernizing Medicine Practice Management | نرم‌افزار اصلاح حرکت | NextGen Healthcare Information Systems EMR | NextGen Healthcare NextGen Practice Management | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار مدیریت بیمار | پایگاه‌های داده موجودی رادیودارو | RamSoft PowerServer RIS/PACS | SOAPware EMR | نرم‌افزار زمان‌بندی | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | نرم‌افزار مرورگر وب | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | mPlexus DICOM RadiX | medQ Q/ris | simplifyMD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخنوری | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | کامپیوتر و الکترونیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک نوشتاری | استدلال قیاسی | بیان نوشتاری | دید نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | سرعت ادراکی | دید دور | تشخیص رنگ بصری | تجسم | سرعت بستار | ثبات دست و بازو | مهارت انگشتان | اصالت | روانی ایده‌ها | توجه انتخابی | حافظه‌سپاری | توانایی عددی | استدلال ریاضی</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | سرعت ادراکی | بینایی دور | تشخیص رنگ بصری | تجسم | سرعت بستار | ثبات دست و بازو | مهارت انگشتان | اصالت | روانی ایده‌ها | توجه انتخابی | حفظ کردن | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | تکرار تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دستان جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض بیماری یا عفونت بودن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | ایمیل | در معرض تابش بودن | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تابش | تماس با دیگران | پیامد خطا | نتایج کاری و خروجی‌های سایر کارکنان | سطح رقابت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | صرف زمان برای نشستن</t>
+          <t>مکالمات تلفنی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | ایمیل | قرار گرفتن در معرض تابش | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | ارتباط با دیگران | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Diagnostic Medical Sonographers | Emergency Medicine Physicians | General Internal Medicine Physicians | Neurodiagnostic Technologists | Neurologists | Nuclear Medicine Technologists | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physicians, Pathologists | Radiation Therapists | Radiologic Technologists and Technicians | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | پزشکان طب اورژانس | پزشکان داخلی عمومی | تکنولوژیست‌های نورودیاگنوستیک | متخصصان مغز و اعصاب | تکنولوژیست‌های پزشکی هسته‌ای | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Physicians, All Other (پزشکان، سایر موارد)</t>
+          <t>پزشکان، سایر موارد (Physicians, All Other)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Attending Physician | Geriatrician | Infectious Disease Physician | Medical Doctor | Nephrologist | Occupational Medicine Physician | Oncologist | Physician | Pulmonologist | Rheumatologist</t>
+          <t>پزشک معالج ارشد | متخصص طب سالمندان | پزشک بیماری‌های عفونی | دکترای پزشکی | متخصص کلیه | پزشک طب کار | متخصص سرطان | پزشک | متخصص ریه | متخصص روماتولوژی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت بودن | نزدیکی فیزیکی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Family Medicine Physicians | General Internal Medicine Physicians | Emergency Medicine Physicians | Pediatricians, General | Cardiologists | Neurologists | Dermatologists | Allergists and Immunologists | Hospitalists | Urologists | Preventive Medicine Physicians | Sports Medicine Physicians | Physical Medicine and Rehabilitation Physicians | Physicians, Pathologists | Psychiatrists | Radiologists | Anesthesiologists | Surgeons, All Other | Physician Assistants | Health Specialties Teachers, Postsecondary</t>
+          <t>پزشکان خانواده | پزشکان داخلی عمومی | پزشکان طب اورژانس | متخصصان کودکان، عمومی | متخصصان قلب | متخصصان مغز و اعصاب | متخصصان پوست | متخصصان آلرژی و ایمونولوژی | پزشکان بیمارستانی | اورولوژیست‌ها | پزشکان طب پیشگیری | پزشکان طب ورزشی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | روان‌پزشکان | رادیولوژیست‌ها | متخصصان بیهوشی | جراحان، سایر | دستیاران پزشک | استادان تخصص‌های بهداشتی، پس از متوسطه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists (متخصصان آلرژی و ایمونولوژی)</t>
+          <t>متخصصان آلرژی و ایمونولوژی (Allergists and Immunologists)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adult and Pediatric Allergy Partner | Allergist | Allergy Physician | Allergy and Immunology Physician | Allergy and Immunology Specialist | Immunologist | Immunology Physician | MD (Medical Doctor) | Pediatric Pulmonologist | Physician</t>
+          <t>متخصص آلرژی بزرگسالان و کودکان | متخصص آلرژی | پزشک آلرژی | پزشک آلرژی و ایمونولوژی | متخصص آلرژی و ایمونولوژی | ایمونولوژیست | پزشک ایمونولوژی | MD (دکترای پزشکی) | متخصص ریه کودکان | پزشک</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | Crowell Systems Medformix | نرم‌افزار پرونده‌های الکترونیک پزشکی و سلامت IMS برای متخصصان آلرژی | نرم‌افزار ایمیل | Epic Practice Management | FlowJo | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | GraphPad Software GraphPad Prism | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Meditab Software AllergyEHR | نرم‌افزار تصویربرداری میکروسکوپ | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | ModuleMD Allergy Module | Molecular Devices Softmax Pro | Mountainside Software Allergy Lab | NextGen Healthcare NextGen Practice Management | نرم‌افزار مدیریت بیمار | Rosch Visionary Systems Visionary Allergy Tracker | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | eClinicalWorks EHR software | simplifyMD</t>
+          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | Crowell Systems Medformix | نرم‌افزار پرونده‌های الکترونیک پزشکی و سلامت IMS برای متخصصان آلرژی | نرم‌افزار ایمیل | Epic Practice Management | FlowJo | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | GraphPad Software GraphPad Prism | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | IOS Health Systems Medios EHR | Kareo Practice Management | McKesson Practice Plus | Meditab Software AllergyEHR | نرم‌افزار تصویربرداری میکروسکوپ | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | ModuleMD Allergy Module | Molecular Devices Softmax Pro | Mountainside Software Allergy Lab | NextGen Healthcare NextGen Practice Management | نرم‌افزار مدیریت بیمار | Rosch Visionary Systems Visionary Allergy Tracker | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | گوش دادن فعال | سخنوری | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | کامپیوتر و الکترونیک | مدیریت و اداره | آموزش و پرورش | پرسنل و منابع انسانی | شیمی | اداری | روان‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | پرسنل و منابع انسانی | شیمی | اداری | روان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | درک نوشتاری | درک شفاهی | استدلال استقرایی | بیان نوشتاری | دید نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | دید دور | اشتراک زمانی | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | تقسیم توجه | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | تماس با دیگران | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض بیماری یا عفونت بودن | پیامد خطا | برخورد با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | سطح رقابت | صرف زمان برای نشستن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | ارتباط با دیگران | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | سطح رقابت | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cardiologists | Chiropractors | Clinical Neuropsychologists | Clinical Nurse Specialists | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Naturopathic Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physicians, Pathologists | Psychiatrists | Urologists</t>
+          <t>متخصصان قلب | کایروپراکتورها | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hospitalists (پزشکان بیمارستانی)</t>
+          <t>پزشکان بیمارستانی (Hospitalists)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Academic Hospitalist | Consultant Physician | Hospitalist | Hospitalist Medical Doctor (Hospitalist MD) | MD (Medical Doctor) | Physician</t>
+          <t>پزشک بیمارستانی دانشگاهی | پزشک مشاور | پزشک بیمارستانی | پزشک بیمارستانی (Hospitalist MD) | MD (دکترای پزشکی) | پزشک</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار صورت‌حساب | نرم‌افزار ورود دستورات پزشک کامپیوتری CPOE | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | MDeverywhere | نرم‌افزار MEDITECH | نرم‌افزار پشتیبانی تصمیم‌گیری پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار مرجع پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار ورود دستورات پزشک به صورت کامپیوتری CPOE | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | MDeverywhere | نرم‌افزار MEDITECH | نرم‌افزار پشتیبانی تصمیم‌گیری پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار مرجع پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | تفکر انتقادی | یادگیری فعال | نظارت | نوشتن | علوم | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | درمان و مشاوره | خدمات مشتری و شخصی | مدیریت و اداره | کامپیوتر و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | درمان و مشاوره | خدمات مشتری و شخصی | مدیریت و اداره | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان شفاهی | درک نوشتاری | درک شفاهی | استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | وضوح گفتار | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | سرعت ادراکی | روانی ایده‌ها | توجه انتخابی | تجسم | حافظه‌سپاری | توانایی عددی | استدلال ریاضی | اصالت | اشتراک زمانی</t>
+          <t>استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | سرعت ادراکی | روانی ایده‌ها | توجه انتخابی | تجسم | حفظ کردن | توانایی عددی | استدلال ریاضی | اصالت | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | تکرار تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | در معرض بیماری یا عفونت بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | نزدیکی فیزیکی | پیامد خطا | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | نتایج کاری و خروجی‌های سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نامه‌ها و یادداشت‌های کتبی | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | پیامد خطا | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نامه‌ها و یادداشت‌های کتبی | سطح رقابت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Anesthesiologists | Cardiologists | Clinical Nurse Specialists | Critical Care Nurses | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Neurologists | Nurse Midwives | Nurse Practitioners | Obstetricians and Gynecologists | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Psychiatrists | Registered Nurses | Urologists</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌شده | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Urologists (اورولوژیست‌ها)</t>
+          <t>اورولوژیست‌ها (Urologists)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Acute Care Physician | MD (Medical Doctor) | Owner | Physician | Practicing Urologist | Surgeon | Urologic Surgeon | Urologist | Urology MD (Urology Medical Doctor)</t>
+          <t>پزشک مراقبت حاد | MD (دکترای پزشکی) | مالک | پزشک | متخصص شاغل اورولوژی | جراح | جراح اورولوژی | متخصص اورولوژی | پزشک اورولوژی (Urology MD)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | Henry Schein Medical Systems MicroMD Urology EMR | IOS Health Systems Medios EHR | Kareo Practice Management | نرم‌افزار MEDITECH | McKesson Practice Plus | Meditwatch Portaflow Advanced | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nextech EMR | SmugMug Flickr | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | eClinicalWorks EHR software | simplifyMD</t>
+          <t>Allscripts PM | Automatic Data Processing AdvancedMD EHR | Benchmark Systems Benchmark Clinical EHR | Bizmatics PrognoCIS EMR | CareCloud Central | Cerner PowerWorks Practice Management | نرم‌افزار ایمیل | Epic Practice Management | Epic Systems | GE Healthcare Centricity Practice Solution | GalacTek ECLIPSE | Greenway Medical Technologies PrimeSUITE | HealthFusion MediTouch | Henry Schein Medical Systems MicroMD Urology EMR | IOS Health Systems Medios EHR | Kareo Practice Management | نرم‌افزار MEDITECH | McKesson Practice Plus | Meditwatch Portaflow Advanced | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Modernizing Medicine Practice Management | NextGen Healthcare NextGen Practice Management | Nextech EMR | SmugMug Flickr | Vitera Healthcare Solutions Vitera Intergy | WRSHealth EMR | athenahealth athenaCollector | نرم‌افزار eClinicalWorks EHR | simplifyMD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نوشتن | سخنوری | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | شیمی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | ریاضیات | اداری | اقتصاد و حسابداری | مخابرات | قانون و دولت | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | شیمی | رایانه و الکترونیک | پرسنل و منابع انسانی | ریاضیات | اداری | اقتصاد و حسابداری | مخابرات | قانون و دولت | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک نوشتاری | بیان نوشتاری | بیان شفاهی | درک شفاهی | استدلال استقرایی | استدلال قیاسی | دید نزدیک | وضوح گفتار | نظم‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | روانی ایده‌ها | دقت کنترل | توجه انتخابی | سرعت بستار | اصالت | سرعت ادراکی | مهارت انگشتان | تشخیص رنگ بصری | مهارت دستی | اشتراک زمانی | حافظه‌سپاری</t>
+          <t>حساسیت به مسئله | درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | روانی ایده‌ها | دقت کنترل | توجه انتخابی | سرعت بستار | اصالت | سرعت ادراکی | مهارت انگشتان | تشخیص رنگ بصری | مهارت دستی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>تماس با دیگران | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | در معرض بیماری یا عفونت بودن | سلامت و ایمنی سایر کارکنان | فشار زمانی | نتایج کاری و خروجی‌های سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف مشابه | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تکرار تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ارتباط با دیگران | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سلامت و ایمنی سایر کارکنان | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Chiropractors | Dermatologists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Naturopathic Physicians | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Oral and Maxillofacial Surgeons | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Radiologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | رادیولوژیست‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0046_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0046_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و تدریس | رایانه و الکترونیک | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | درمان و مشاوره | آموزش و پرورش | رایانه و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری در نتیجه‌گیری | وضوح گفتار | طبقه‌بندی منعطف | روانی ایده‌ها | سرعت ادراک | تجسم فضایی | ابتکار | توجه انتخابی | سرعت در نتیجه‌گیری | کار با اعداد | استدلال ریاضی</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | تجسم | اصالت | توجه انتخابی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب و عروق | کایروپراکتورها | متخصصان روان‌شناسی اعصاب بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | روان‌شناسان اعصاب | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | چشم‌پزشکان، غیر از کودکان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان عصب‌روان‌شناسی بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان عصب‌روان‌شناسی | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | رایانه و الکترونیک | آموزش و تدریس | شیمی | امور دفتری و اداری | مدیریت و امور اداری | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | رایانه و الکترونیک | آموزش و پرورش | شیمی | اداری | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | دید نزدیک | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | ثبات دست و بازو | طبقه‌بندی منعطف | انعطاف‌پذیری در نتیجه‌گیری | ابتکار | روانی ایده‌ها | چابکی انگشتان | چابکی دستی | توجه انتخابی | تشخیص رنگ‌ها | دقت کنترل حرکتی | تقسیم توجه | سرعت ادراک | سرعت در نتیجه‌گیری</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | مهارت انگشتان | مهارت دستی | توجه انتخابی | تشخیص رنگ بصری | دقت کنترل | تقسیم توجه | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب و عروق | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان مقیم بیمارستان | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب | ماماها | پرستاران پیشرفته بالینی | چشم‌پزشکان، غیر از کودکان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران رسمی | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | علوم پایه | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس | امور پرسنلی و منابع انسانی | رایانه و الکترونیک | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | درمان و مشاوره | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | دید نزدیک | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری | تقسیم توجه | سرعت ادراک | طبقه‌بندی منعطف | ابتکار | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روان‌پزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان قلب و عروق | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان مقیم بیمارستان | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب | ماماها | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | علوم پایه | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | شیمی | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | دید نزدیک | وضوح گفتار | مرتب‌سازی اطلاعات | طبقه‌بندی منعطف | انعطاف‌پذیری در نتیجه‌گیری | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | سرعت در نتیجه‌گیری | تشخیص رنگ‌ها | سرعت ادراک | کار با اعداد | استدلال ریاضی | ابتکار</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | متخصصان روان‌شناسی اعصاب بالینی | کارشناسان ژنتیک سلولی | کارشناسان سیتوتکنولوژی | متخصصان پوست و مو | پزشکان طب اورژانس | متخصصان بیماری‌های داخلی | کارشناسان بافت‌شناسی | دانشمندان علوم پزشکی، غیر از همه‌گیرشناسان | کاردان‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | متخصصان مغز و اعصاب | چشم‌پزشکان، غیر از کودکان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان رادیولوژی | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | متخصصان عصب‌روان‌شناسی بالینی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | متخصصان مغز و اعصاب | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان رادیولوژی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری | فلسفه و الهیات | رایانه و الکترونیک</t>
+          <t>درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | طبقه‌بندی منعطف | مرتب‌سازی اطلاعات | دید نزدیک | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری | ابتکار | توجه انتخابی | حافظه | سرعت در نتیجه‌گیری</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی | حفظ کردن | سرعت بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران پیشرفته روان‌پزشکی | متخصصان قلب و عروق | متخصصان روان‌شناسی اعصاب بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | مشاوران ژنتیک | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب | روان‌شناسان اعصاب | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | تکنسین‌های روان‌پزشکی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیماری‌های قلب و عروق | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | متخصصان عصب‌روان‌شناسی | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | تکنسین‌های روان‌پزشکی و بهداشت روان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس | خدمات مشتریان و خدمات فردی | فیزیک</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری | وضوح گفتار | مرتب‌سازی اطلاعات | طبقه‌بندی منعطف | تشخیص گفتار | سرعت ادراک | دید دور | تشخیص رنگ‌ها | تجسم فضایی | سرعت در نتیجه‌گیری | ثبات دست و بازو | چابکی انگشتان | ابتکار | روانی ایده‌ها | توجه انتخابی | حافظه | کار با اعداد | استدلال ریاضی</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | سرعت ادراکی | بینایی دور | تشخیص رنگ بصری | تجسم | سرعت بستار | ثبات دست و بازو | مهارت انگشتان | اصالت | روانی ایده‌ها | توجه انتخابی | حفظ کردن | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سونوگرافی تشخیصی | پزشکان طب اورژانس | متخصصان بیماری‌های داخلی | کارشناسان فناوری تشخیص اعصاب | متخصصان مغز و اعصاب | کارشناسان طب هسته‌ای | متخصصان زنان و زایمان | چشم‌پزشکان، غیر از کودکان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | کارشناسان پرتودرمانی (رادیوتراپی) | کارشناسان و تکنسین‌های رادیولوژی | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | تکنسین‌های الکترونورودیاگنوستیک | متخصصان مغز و اعصاب | کارشناسان و تکنسین‌های پزشکی هسته‌ای | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | درمان و مشاوره | آموزش و تدریس | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | درمان و مشاوره | آموزش و پرورش | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | طبقه‌بندی منعطف | تجسم فضایی | تقسیم توجه</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان طب اورژانس | متخصصان عمومی کودکان | متخصصان قلب و عروق | متخصصان مغز و اعصاب | متخصصان پوست و مو | متخصصان آلرژی و ایمنی‌شناسی | پزشکان مقیم بیمارستان | متخصصان اورولوژی | متخصصان طب پیشگیری | متخصصان طب ورزشی | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | روان‌پزشکان | متخصصان رادیولوژی | متخصصان بیهوشی | جراحان، سایر تخصص‌ها | دستیاران پزشک | مدرسان رشته‌های تخصصی علوم پزشکی، دانشگاهی</t>
+          <t>پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب اورژانس | متخصصان عمومی کودکان | متخصصان بیماری‌های قلب و عروق | متخصصان مغز و اعصاب | متخصصان پوست و مو | متخصصان آلرژی و ایمنی‌شناسی | پزشکان مقیم بیمارستان | متخصصان اورولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری | پزشکان طب ورزشی | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | روان‌پزشکان | متخصصان رادیولوژی | متخصصان بیهوشی | سایر جراحان | دستیاران پزشک | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | علوم پایه | راهبردهای یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | آموزش و تدریس | امور پرسنلی و منابع انسانی | شیمی | امور دفتری و اداری | روان‌شناسی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | پرسنل و منابع انسانی | شیمی | اداری | روان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان کتبی | دید نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | طبقه‌بندی منعطف | ابتکار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در نتیجه‌گیری | دید دور | تقسیم توجه | سرعت ادراک | سرعت در نتیجه‌گیری | کار با اعداد | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | تقسیم توجه | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | کایروپراکتورها | متخصصان روان‌شناسی اعصاب بالینی | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | چشم‌پزشکان، غیر از کودکان | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | آموزش و تدریس | درمان و مشاوره | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | درمان و مشاوره | خدمات مشتری و شخصی | مدیریت و اداره | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | طبقه‌بندی منعطف | انعطاف‌پذیری در نتیجه‌گیری | سرعت در نتیجه‌گیری | سرعت ادراک | روانی ایده‌ها | توجه انتخابی | تجسم فضایی | حافظه | کار با اعداد | استدلال ریاضی | ابتکار | تقسیم توجه</t>
+          <t>استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | سرعت ادراکی | روانی ایده‌ها | توجه انتخابی | تجسم | حفظ کردن | توانایی عددی | استدلال ریاضی | اصالت | تقسیم توجه</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران پیشرفته روان‌پزشکی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه (ICU) | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب | ماماها | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | پرستاران رسمی | متخصصان اورولوژی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | پرستاران | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و تدریس | درمان و مشاوره | مدیریت و امور اداری | روان‌شناسی | خدمات مشتریان و خدمات فردی | شیمی | رایانه و الکترونیک | امور پرسنلی و منابع انسانی | ریاضیات | امور دفتری و اداری | اقتصاد و حسابداری | ارتباطات و مخابرات | حقوق و مقررات دولتی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | مدیریت و اداره | روان‌شناسی | خدمات مشتری و شخصی | شیمی | رایانه و الکترونیک | پرسنل و منابع انسانی | ریاضیات | اداری | اقتصاد و حسابداری | مخابرات | قانون و دولت | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | استدلال استقرایی | استدلال قیاسی | دید نزدیک | وضوح گفتار | مرتب‌سازی اطلاعات | تشخیص گفتار | طبقه‌بندی منعطف | انعطاف‌پذیری در نتیجه‌گیری | ثبات دست و بازو | روانی ایده‌ها | دقت کنترل حرکتی | توجه انتخابی | سرعت در نتیجه‌گیری | ابتکار | سرعت ادراک | چابکی انگشتان | تشخیص رنگ‌ها | چابکی دستی | تقسیم توجه | حافظه</t>
+          <t>حساسیت به مسئله | درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | روانی ایده‌ها | دقت کنترل | توجه انتخابی | سرعت بستار | اصالت | سرعت ادراکی | مهارت انگشتان | تشخیص رنگ بصری | مهارت دستی | تقسیم توجه | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب و عروق | کایروپراکتورها | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان خانواده | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب | پرستاران پیشرفته بالینی | متخصصان زنان و زایمان | چشم‌پزشکان، غیر از کودکان | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از کودکان | جراحان کودکان | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
